--- a/products-storage/06-id-blokiruet-oplatu/06-reestr-zamechaniy.xlsx
+++ b/products-storage/06-id-blokiruet-oplatu/06-reestr-zamechaniy.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="E6" s="2">
-        <f>СЧЁТЕСЛИ(G2:G20;"В работе")</f>
+        <f>COUNTIF(G2:G20,"В работе")</f>
         <v/>
       </c>
       <c r="F6" s="2" t="inlineStr"/>

--- a/products-storage/06-id-blokiruet-oplatu/06-reestr-zamechaniy.xlsx
+++ b/products-storage/06-id-blokiruet-oplatu/06-reestr-zamechaniy.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIF(G2:G20,"В работе")</f>
+        <f>СЧЁТЕСЛИ(G2:G20;"В работе")</f>
         <v/>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
